--- a/partner_results/unknown_complete/ClassMoreThanOneEnglishDefinition_unknown.xlsx
+++ b/partner_results/unknown_complete/ClassMoreThanOneEnglishDefinition_unknown.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ultrasonic cleaner</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cleaning device</t>
+          <t>completely executed planned process</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A device that uses ultrasound and a cleaning solvent to clean delicate or complex items. | An Ultrasonic Cleaner is a Cleaning Device that uses high-frequency sound waves and a cleaning solvent to remove contaminants from delicate or complex items.</t>
+          <t>a planned process with objective to check that the accuracy or the quality of a claim or prediction  satisfies some criteria and which is assessed by comparing with independent results | a planned process with objective to check that the accuracy or the quality of a claim or prediction satisfies some criteria and which is assessed by comparing with independent results</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>grain boundary</t>
+          <t>glass-ceramic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fiat surface</t>
+          <t>engineered material</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>the part of a grain that is close to the grain boundary and possibly characterized by disorder is a fiat object part (grain surface layer) | A grain boundary is a fiat surface that separates adjacent grains in a polycrystalline material and is characterized by structural discontinuity.</t>
+          <t>Glass‑ceramics are inorganic, non‑metallic materials prepared by controlled crystallization of glasses via different processing methods; they contain at least one type of functional crystalline phase and a residual glass, and the crystallized volume fraction may vary from ppm to almost 100%. | engenieered material that is inorganic, non‑metallic and prepared by controlled crystallization of glasses via different processing methods; they contain at least one type of functional crystalline phase and a residual glass, and the crystallized volume fraction may vary from ppm to almost 100%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,18 +484,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chemical entity</t>
+          <t>grain boundary</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>fiat surface</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A chemical entity is a physical entity of interest in chemistry including molecular entities, parts thereof, and chemical substances.</t>
+          <t>the part of a grain that is close to the grain boundary and possibly characterized by disorder is a fiat object part (grain surface layer) | A grain boundary is a fiat surface that separates adjacent grains in a polycrystalline material and is characterized by structural discontinuity.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,22 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>microtome</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>directive information entity</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Alan Ruttenberg</t>
-        </is>
-      </c>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A directive information entity with action specifications and objective specifications as parts, and that may be concretized as a realizable entity that, if realized, is realized in a process in which the bearer tries to achieve the objectives by taking the actions specified. | A directive information entity with action specifications and objective specifications as parts, and that may be concretized as a realizable entity that, if realized, is realized in a process in which the bearer tries to achieve the objectives by taking the actions specified.</t>
+          <t>A device used to cut extremely thin slices of material, often for microscopic examination. | A Microtome is a Measuring Device that cuts extremely thin slices of material, often for examination under a microscope.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -526,18 +522,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>biocompatibility analyzing process</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>realizable entity</t>
+          <t>biological property analyzing process</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts. | (Elucidation) A role b is a realizable entity such that b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to be &amp; b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed</t>
+          <t>An example of a biocompatibility analyzing process is an in vitro cell culture test, where cells are cultured in the presence of the implant material to observe any cytotoxic effects, such as changes in cell morphology, proliferation rate, or cell viability. | A biological property analyzing process that evaluates the compatibility of a material with living tissues to ensure it does not provoke an adverse biological response.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -545,18 +541,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>ultrasonic cleaner</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>independent continuant</t>
+          <t>cleaning device</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time. | (Elucidation) A material entity is an independent continuant has some portion of matter as continuant part</t>
+          <t>An Ultrasonic Cleaner is a Cleaning Device that uses high-frequency sound waves and a cleaning solvent to remove contaminants from delicate or complex items. | A device that uses ultrasound and a cleaning solvent to clean delicate or complex items.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -564,18 +560,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>microtome</t>
+          <t>chemical entity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A Microtome is a Measuring Device that cuts extremely thin slices of material, often for examination under a microscope. | A device used to cut extremely thin slices of material, often for microscopic examination.</t>
+          <t>A chemical entity is a physical entity of interest in chemistry including molecular entities, parts thereof, and chemical substances.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -583,18 +579,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>natural organic material</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>chemical entity</t>
+          <t>material</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Any constitutionally or isotopically distinct atom, molecule, ion, ion pair, radical, radical ion, complex, conformer etc., identifiable as a separately distinguishable entity.</t>
+          <t>material derived from natural biological sources or processes | Natural organic materials are materials derived from natural biological sources, primarily composed of carbon-based compounds.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -602,18 +598,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fused silica glass</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>silicate glass</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>silicate glass that is essentially pure, amorphous SiO₂ | optical glass that is made from pure silica, prized for its high transparency and thermal stability.|Fused silica is a silicate glass that is essentially pure, amorphous SiO₂</t>
+          <t>A person or organization that has a manufacturer role. | A person or organization that has a manufacturer role</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -621,7 +617,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -629,10 +625,14 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PERSON: Susanna Sansone</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A person or organization that has a manufacturer role | A person or organization that has a manufacturer role.</t>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members. | An organization is an immaterial entity that has the organisation role and there exists some sort of legal framework that recognises the entity and its continued existence.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -640,18 +640,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>glass-ceramic</t>
+          <t>electron microscope</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>engineered material</t>
+          <t>microscope</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>engenieered material that is inorganic, non‑metallic and prepared by controlled crystallization of glasses via different processing methods; they contain at least one type of functional crystalline phase and a residual glass, and the crystallized volume fraction may vary from ppm to almost 100% | Glass‑ceramics are inorganic, non‑metallic materials prepared by controlled crystallization of glasses via different processing methods; they contain at least one type of functional crystalline phase and a residual glass, and the crystallized volume fraction may vary from ppm to almost 100%.</t>
+          <t>A microscope that uses a beam of electrons to create high-resolution images of a sample's surface or structure. | An electron-optical instrument in which a beam of electrons is used to produce an enlarged image of a minute object.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -659,18 +659,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>electron microscope</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>microscope</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A microscope that uses a beam of electrons to create high-resolution images of a sample's surface or structure. | An electron-optical instrument in which a beam of electrons is used to produce an enlarged image of a minute object.</t>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts. | (Elucidation) A role b is a realizable entity such that b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to be &amp; b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -678,22 +678,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>fused silica glass</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>material entity</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PERSON: Bjoern Peters</t>
-        </is>
-      </c>
+          <t>optical glass</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members. | An organization is an immaterial entity that has the organisation role and there exists some sort of legal framework that recognises the entity and its continued existence.</t>
+          <t>optical glass that is made from pure silica, prized for its high transparency and thermal stability.|Fused silica is a silicate glass that is essentially pure, amorphous SiO₂ | silicate glass that is essentially pure, amorphous SiO₂</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -701,18 +697,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cryogenic freezer</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>temperature change device</t>
+          <t>portion of matter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A device used to preserve materials at extremely low temperatures, typically below -150°C. | A cryogenic freezer is a temperature change device that preserves materials at extremely low temperatures, often below -150°C.</t>
+          <t>A chemical substance is a portion of matter of constant composition, composed of molecular entities of the same type or of different types.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -720,18 +716,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>natural organic material</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>directive information entity</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Clint Dowland</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Natural organic materials are materials derived from natural biological sources, primarily composed of carbon-based compounds. | material derived from natural biological sources or processes</t>
+          <t>A directive information entity with action specifications and objective specifications as parts, and that may be concretized as a realizable entity that, if realized, is realized in a process in which the bearer tries to achieve the objectives by taking the actions specified. | A directive information entity with action specifications and objective specifications as parts, and that may be concretized as a realizable entity that, if realized, is realized in a process in which the bearer tries to achieve the objectives by taking the actions specified.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -739,18 +739,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>cryogenic freezer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>portion of matter</t>
+          <t>temperature change device</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A chemical substance is a portion of matter of constant composition, composed of molecular entities of the same type or of different types.</t>
+          <t>A device used to preserve materials at extremely low temperatures, typically below -150°C. | A cryogenic freezer is a temperature change device that preserves materials at extremely low temperatures, often below -150°C.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -758,22 +758,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>completely executed planned process</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PlanAndPlannedProcess Branch</t>
-        </is>
-      </c>
+          <t>independent continuant</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A planned process that has the objective to produce information about a material entity (the evaluant) by examining it. | A planned process with the objective to produce information about the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time. | (Elucidation) A material entity is an independent continuant has some portion of matter as continuant part</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -781,40 +777,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>completely executed planned process</t>
+          <t>chemical entity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>a planned process with objective to check that the accuracy or the quality of a claim or prediction satisfies some criteria and which is assessed by comparing with independent results | a planned process with objective to check that the accuracy or the quality of a claim or prediction  satisfies some criteria and which is assessed by comparing with independent results</t>
+          <t>Any constitutionally or isotopically distinct atom, molecule, ion, ion pair, radical, radical ion, complex, conformer etc., identifiable as a separately distinguishable entity.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>biocompatibility analyzing process</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>biological property analyzing process</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>A biological property analyzing process that evaluates the compatibility of a material with living tissues to ensure it does not provoke an adverse biological response. | An example of a biocompatibility analyzing process is an in vitro cell culture test, where cells are cultured in the presence of the implant material to observe any cytotoxic effects, such as changes in cell morphology, proliferation rate, or cell viability.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
